--- a/単語/単語14.xlsx
+++ b/単語/単語14.xlsx
@@ -446,1207 +446,1207 @@
   <dimension ref="A1:B100"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="46" customWidth="1" min="1" max="1"/>
-    <col width="26" customWidth="1" min="2" max="2"/>
+    <col width="52" customWidth="1" min="1" max="1"/>
+    <col width="29" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>AにBを思い出させる</t>
+          <t>家に帰る途中で</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>remind A of B</t>
+          <t>on one's [the] way home</t>
         </is>
       </c>
     </row>
     <row r="2" ht="20" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Aを置き忘れる、Aを後に残す</t>
+          <t>〜の真向かいに、〜の向こう側に</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>leave A behind</t>
+          <t>across from ~</t>
         </is>
       </c>
     </row>
     <row r="3" ht="20" customHeight="1">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>（意見・考えが）〜と一致する、〜に同意する</t>
+          <t>しばらくして</t>
         </is>
       </c>
       <c r="B3" s="1" t="inlineStr">
         <is>
-          <t>agree with ~</t>
+          <t>after a while</t>
         </is>
       </c>
     </row>
     <row r="4" ht="20" customHeight="1">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>〜するのが簡単である</t>
+          <t>留守にする</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>be simple to do</t>
+          <t>be away</t>
         </is>
       </c>
     </row>
     <row r="5" ht="20" customHeight="1">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>基準によって</t>
+          <t>〜から出る、（車など）を降りる</t>
         </is>
       </c>
       <c r="B5" s="1" t="inlineStr">
         <is>
-          <t>by standard</t>
+          <t>get out of ~</t>
         </is>
       </c>
     </row>
     <row r="6" ht="20" customHeight="1">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>Aが〜するのを妨げる［防ぐ］</t>
+          <t>〜する機会を持つ</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>prevent A from doing</t>
+          <t>have a chance to do</t>
         </is>
       </c>
     </row>
     <row r="7" ht="20" customHeight="1">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>〜を誇りに思っている</t>
+          <t>〜と偶然出会う</t>
         </is>
       </c>
       <c r="B7" s="1" t="inlineStr">
         <is>
-          <t>be proud of ~</t>
+          <t>run into ~</t>
         </is>
       </c>
     </row>
     <row r="8" ht="20" customHeight="1">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>本を作る</t>
+          <t>よく眠る</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>make book</t>
+          <t>sleep well</t>
         </is>
       </c>
     </row>
     <row r="9" ht="20" customHeight="1">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>スピーチをする</t>
+          <t>いつか別のときに</t>
         </is>
       </c>
       <c r="B9" s="1" t="inlineStr">
         <is>
-          <t>make a speech</t>
+          <t>some other time</t>
         </is>
       </c>
     </row>
     <row r="10" ht="20" customHeight="1">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>Aと結婚している</t>
+          <t>BからAを取り出す</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>be married to A</t>
+          <t>take A out of B</t>
         </is>
       </c>
     </row>
     <row r="11" ht="20" customHeight="1">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>〜に特有である、〜だけの</t>
+          <t>〜の病気にかかる、〜に苦しむ</t>
         </is>
       </c>
       <c r="B11" s="1" t="inlineStr">
         <is>
-          <t>be unique to ~</t>
+          <t>suffer from ~</t>
         </is>
       </c>
     </row>
     <row r="12" ht="20" customHeight="1">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>（〜のそばを）通り過ぎる</t>
+          <t>特に</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>pass by (~)</t>
+          <t>in particular</t>
         </is>
       </c>
     </row>
     <row r="13" ht="20" customHeight="1">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>仕事で、商用で</t>
+          <t>〜に基づいている</t>
         </is>
       </c>
       <c r="B13" s="1" t="inlineStr">
         <is>
-          <t>on business</t>
+          <t>be based on ~</t>
         </is>
       </c>
     </row>
     <row r="14" ht="20" customHeight="1">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>次から次へと、続々と</t>
+          <t>〜を持ち［連れ］帰る</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>one after another</t>
+          <t>bring back ~</t>
         </is>
       </c>
     </row>
     <row r="15" ht="20" customHeight="1">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>AをBと共有する［分かち合う］</t>
+          <t>もはや〜ない</t>
         </is>
       </c>
       <c r="B15" s="1" t="inlineStr">
         <is>
-          <t>share A with B</t>
+          <t>no longer ~</t>
         </is>
       </c>
     </row>
     <row r="16" ht="20" customHeight="1">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>〜に注意を払う</t>
+          <t>〜次第である、〜に依存する</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>pay attention to ~</t>
+          <t>depend on ~</t>
         </is>
       </c>
     </row>
     <row r="17" ht="20" customHeight="1">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>来る日も来る日も</t>
+          <t>〜を取り除く</t>
         </is>
       </c>
       <c r="B17" s="1" t="inlineStr">
         <is>
-          <t>day after day</t>
+          <t>get rid of ~</t>
         </is>
       </c>
     </row>
     <row r="18" ht="20" customHeight="1">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>〜で混雑している</t>
+          <t>〜に出かける、〜に向けて出発する</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>be crowded with ~</t>
+          <t>leave for ~</t>
         </is>
       </c>
     </row>
     <row r="19" ht="20" customHeight="1">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>〜を扱う、〜に処理する</t>
+          <t>〜のスイッチを入れる</t>
         </is>
       </c>
       <c r="B19" s="1" t="inlineStr">
         <is>
-          <t>deal with ~</t>
+          <t>turn on ~</t>
         </is>
       </c>
     </row>
     <row r="20" ht="20" customHeight="1">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>（〜しようと）努力する</t>
+          <t>結局〜に終わる</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>make an effort (to do)</t>
+          <t>result in ~</t>
         </is>
       </c>
     </row>
     <row r="21" ht="20" customHeight="1">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>何度も繰り返して</t>
+          <t>〜に関係がある</t>
         </is>
       </c>
       <c r="B21" s="1" t="inlineStr">
         <is>
-          <t>over and over (again)</t>
+          <t>be related to ~</t>
         </is>
       </c>
     </row>
     <row r="22" ht="20" customHeight="1">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>共通の、共通に</t>
+          <t>いつでも、その間ずっと</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>in common</t>
+          <t>all the time</t>
         </is>
       </c>
     </row>
     <row r="23" ht="20" customHeight="1">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>〜次第である、〜に頼る</t>
+          <t>しばらくの間</t>
         </is>
       </c>
       <c r="B23" s="1" t="inlineStr">
         <is>
-          <t>depend on ~</t>
+          <t>for a while</t>
         </is>
       </c>
     </row>
     <row r="24" ht="20" customHeight="1">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>それにもかかわらず、しかし</t>
+          <t>〜の終わりまでには</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>and yet</t>
+          <t>by the end of ~</t>
         </is>
       </c>
     </row>
     <row r="25" ht="20" customHeight="1">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>気兼ねなくくつろぐ</t>
+          <t>電話を切らないでおく、ちょっと待つ</t>
         </is>
       </c>
       <c r="B25" s="1" t="inlineStr">
         <is>
-          <t>feel at home</t>
+          <t>hold on</t>
         </is>
       </c>
     </row>
     <row r="26" ht="20" customHeight="1">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>〜であることがわかる、結局〜になる</t>
+          <t>〜を満たす、〜をいっぱいにする</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>turn out (to be) ~</t>
+          <t>fill up ~</t>
         </is>
       </c>
     </row>
     <row r="27" ht="20" customHeight="1">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>〜するのが習慣である</t>
+          <t>言い換えれば</t>
         </is>
       </c>
       <c r="B27" s="1" t="inlineStr">
         <is>
-          <t>be custom to do</t>
+          <t>in other words</t>
         </is>
       </c>
     </row>
     <row r="28" ht="20" customHeight="1">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>〜を笑う</t>
+          <t>順番に</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>laugh at ~</t>
+          <t>in turn</t>
         </is>
       </c>
     </row>
     <row r="29" ht="20" customHeight="1">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>〜を表す、〜を象徴する</t>
+          <t>〜を指摘する</t>
         </is>
       </c>
       <c r="B29" s="1" t="inlineStr">
         <is>
-          <t>stand for ~</t>
+          <t>point out ~</t>
         </is>
       </c>
     </row>
     <row r="30" ht="20" customHeight="1">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>〜に依存する、〜次第である</t>
+          <t>結局（は）</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>depend upon ~</t>
+          <t>after all</t>
         </is>
       </c>
     </row>
     <row r="31" ht="20" customHeight="1">
       <c r="A31" s="1" t="inlineStr">
         <is>
-          <t>〜に集中する</t>
+          <t>長い間</t>
         </is>
       </c>
       <c r="B31" s="1" t="inlineStr">
         <is>
-          <t>concentrate on ~</t>
+          <t>for long</t>
         </is>
       </c>
     </row>
     <row r="32" ht="20" customHeight="1">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>最高速度で</t>
+          <t>（物事が）うまくいかない、（機械などが）故障する</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>at top speed</t>
+          <t>go wrong</t>
         </is>
       </c>
     </row>
     <row r="33" ht="20" customHeight="1">
       <c r="A33" s="1" t="inlineStr">
         <is>
-          <t>動的である、活気に満ちている</t>
+          <t>一直線に、整列して</t>
         </is>
       </c>
       <c r="B33" s="1" t="inlineStr">
         <is>
-          <t>be dynamic</t>
+          <t>in line</t>
         </is>
       </c>
     </row>
     <row r="34" ht="20" customHeight="1">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>〜と仲良くやっていく</t>
+          <t>（〜の）お返しに</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>get along with ~</t>
+          <t>in return (for ~)</t>
         </is>
       </c>
     </row>
     <row r="35" ht="20" customHeight="1">
       <c r="A35" s="1" t="inlineStr">
         <is>
-          <t>亡くなる</t>
+          <t>〜を見る</t>
         </is>
       </c>
       <c r="B35" s="1" t="inlineStr">
         <is>
-          <t>pass away</t>
+          <t>take [have] a look at ~</t>
         </is>
       </c>
     </row>
     <row r="36" ht="20" customHeight="1">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>〜を指さす、〜を指し示す</t>
+          <t>…であろうとなかろうと</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>point to [at] ~</t>
+          <t>whether ... or not</t>
         </is>
       </c>
     </row>
     <row r="37" ht="20" customHeight="1">
       <c r="A37" s="1" t="inlineStr">
         <is>
-          <t>AをBと引き離す［分ける］</t>
+          <t>〜を誇りに思う</t>
         </is>
       </c>
       <c r="B37" s="1" t="inlineStr">
         <is>
-          <t>separate A from B</t>
+          <t>be proud of ~</t>
         </is>
       </c>
     </row>
     <row r="38" ht="20" customHeight="1">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>〜に変わる、〜になる</t>
+          <t>売り切れている</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>turn into ~</t>
+          <t>be sold out</t>
         </is>
       </c>
     </row>
     <row r="39" ht="20" customHeight="1">
       <c r="A39" s="1" t="inlineStr">
         <is>
-          <t>〜に特有である</t>
+          <t>〜でいっぱいである</t>
         </is>
       </c>
       <c r="B39" s="1" t="inlineStr">
         <is>
-          <t>be specific to ~</t>
+          <t>be full of ~</t>
         </is>
       </c>
     </row>
     <row r="40" ht="20" customHeight="1">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>AかBか、AであろうとBであろうと</t>
+          <t>（車など）に乗る</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>whether A or B</t>
+          <t>get in ~</t>
         </is>
       </c>
     </row>
     <row r="41" ht="20" customHeight="1">
       <c r="A41" s="1" t="inlineStr">
         <is>
-          <t>AにBを警告する</t>
+          <t>集まる</t>
         </is>
       </c>
       <c r="B41" s="1" t="inlineStr">
         <is>
-          <t>warn A against B</t>
+          <t>get together</t>
         </is>
       </c>
     </row>
     <row r="42" ht="20" customHeight="1">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>気楽にやる</t>
+          <t>（最上級を強めて）断然</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>take it easy</t>
+          <t>by far</t>
         </is>
       </c>
     </row>
     <row r="43" ht="20" customHeight="1">
       <c r="A43" s="1" t="inlineStr">
         <is>
-          <t>〜に対して厳しい</t>
+          <t>確かに</t>
         </is>
       </c>
       <c r="B43" s="1" t="inlineStr">
         <is>
-          <t>be strict with ~</t>
+          <t>for sure</t>
         </is>
       </c>
     </row>
     <row r="44" ht="20" customHeight="1">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>〜に成功する</t>
+          <t>〜を失望させる、〜を下げる</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>succeed in ~</t>
+          <t>let ~ down</t>
         </is>
       </c>
     </row>
     <row r="45" ht="20" customHeight="1">
       <c r="A45" s="1" t="inlineStr">
         <is>
-          <t>標準的である</t>
+          <t>決心する</t>
         </is>
       </c>
       <c r="B45" s="1" t="inlineStr">
         <is>
-          <t>be standard</t>
+          <t>make up one's mind</t>
         </is>
       </c>
     </row>
     <row r="46" ht="20" customHeight="1">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>すでにもはや〜ない</t>
+          <t>〜に似ている</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>no longer ~</t>
+          <t>take after ~</t>
         </is>
       </c>
     </row>
     <row r="47" ht="20" customHeight="1">
       <c r="A47" s="1" t="inlineStr">
         <is>
-          <t>Aの基礎をBに置く</t>
+          <t>〜であることがわかる</t>
         </is>
       </c>
       <c r="B47" s="1" t="inlineStr">
         <is>
-          <t>base A on B</t>
+          <t>turn out to be ~</t>
         </is>
       </c>
     </row>
     <row r="48" ht="20" customHeight="1">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>意味をなす、理にかなっている</t>
+          <t>運が良ければ</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>make sense</t>
+          <t>with luck</t>
         </is>
       </c>
     </row>
     <row r="49" ht="20" customHeight="1">
       <c r="A49" s="1" t="inlineStr">
         <is>
-          <t>故障する、〜を分解する</t>
+          <t>〜に反対である</t>
         </is>
       </c>
       <c r="B49" s="1" t="inlineStr">
         <is>
-          <t>break down (~)</t>
+          <t>be against ~</t>
         </is>
       </c>
     </row>
     <row r="50" ht="20" customHeight="1">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>〜を専攻する</t>
+          <t>チェックアウトする</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>major in ~</t>
+          <t>check out</t>
         </is>
       </c>
     </row>
     <row r="51" ht="20" customHeight="1">
       <c r="A51" s="1" t="inlineStr">
         <is>
-          <t>〜に追いつく</t>
+          <t>万一に備えて</t>
         </is>
       </c>
       <c r="B51" s="1" t="inlineStr">
         <is>
-          <t>catch up with ~</t>
+          <t>(just) in case</t>
         </is>
       </c>
     </row>
     <row r="52" ht="20" customHeight="1">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>AをBで満たす</t>
+          <t>人前で、公衆の面前で</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>fill A with B</t>
+          <t>in public</t>
         </is>
       </c>
     </row>
     <row r="53" ht="20" customHeight="1">
       <c r="A53" s="1" t="inlineStr">
         <is>
-          <t>多かれ少なかれ、だいたい</t>
+          <t>〜にざっと目を通す</t>
         </is>
       </c>
       <c r="B53" s="1" t="inlineStr">
         <is>
-          <t>more or less</t>
+          <t>look through ~</t>
         </is>
       </c>
     </row>
     <row r="54" ht="20" customHeight="1">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>〜に不可欠である</t>
+          <t>今や…なので</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>be essential to ~</t>
+          <t>now that ...</t>
         </is>
       </c>
     </row>
     <row r="55" ht="20" customHeight="1">
       <c r="A55" s="1" t="inlineStr">
         <is>
-          <t>〜に身を投じる、〜に没頭する</t>
+          <t>自分自身の</t>
         </is>
       </c>
       <c r="B55" s="1" t="inlineStr">
         <is>
-          <t>throw oneself into ~</t>
+          <t>of one's own</t>
         </is>
       </c>
     </row>
     <row r="56" ht="20" customHeight="1">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>Aに〜させない、Aが〜するのを防ぐ</t>
+          <t>たくさんの〜</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>keep A from doing</t>
+          <t>plenty of ~</t>
         </is>
       </c>
     </row>
     <row r="57" ht="20" customHeight="1">
       <c r="A57" s="1" t="inlineStr">
         <is>
-          <t>突然泣き出す</t>
+          <t>ゆっくりやる</t>
         </is>
       </c>
       <c r="B57" s="1" t="inlineStr">
         <is>
-          <t>burst into tears</t>
+          <t>take one's time</t>
         </is>
       </c>
     </row>
     <row r="58" ht="20" customHeight="1">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>〜と恋に落ちる</t>
+          <t>病気で寝ている</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>fall in love with ~</t>
+          <t>be sick in bed</t>
         </is>
       </c>
     </row>
     <row r="59" ht="20" customHeight="1">
       <c r="A59" s="1" t="inlineStr">
         <is>
-          <t>Aに〜することを気づかせる</t>
+          <t>Aを車に乗せる</t>
         </is>
       </c>
       <c r="B59" s="1" t="inlineStr">
         <is>
-          <t>remind A to do</t>
+          <t>give A a ride</t>
         </is>
       </c>
     </row>
     <row r="60" ht="20" customHeight="1">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>〜は別として、〜から離れて</t>
+          <t>（距離・進行の度合いが）どのくらい…</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>apart from ~</t>
+          <t>how far ...</t>
         </is>
       </c>
     </row>
     <row r="61" ht="20" customHeight="1">
       <c r="A61" s="1" t="inlineStr">
         <is>
-          <t>〜とまったく同じである</t>
+          <t>実現する</t>
         </is>
       </c>
       <c r="B61" s="1" t="inlineStr">
         <is>
-          <t>be identical to ~</t>
+          <t>come true</t>
         </is>
       </c>
     </row>
     <row r="62" ht="20" customHeight="1">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>〜について言えば</t>
+          <t>〜の最後に</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>as for ~</t>
+          <t>at [in] the end of ~</t>
         </is>
       </c>
     </row>
     <row r="63" ht="20" customHeight="1">
       <c r="A63" s="1" t="inlineStr">
         <is>
-          <t>〜を処分する［取り除く］</t>
+          <t>（Aが）〜するのに…かかる</t>
         </is>
       </c>
       <c r="B63" s="1" t="inlineStr">
         <is>
-          <t>get rid of ~</t>
+          <t>It takes (A) ... to do</t>
         </is>
       </c>
     </row>
     <row r="64" ht="20" customHeight="1">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>〜をもたらす［引き起こす］</t>
+          <t>演説をする</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>bring about ~</t>
+          <t>make [give] a speech</t>
         </is>
       </c>
     </row>
     <row r="65" ht="20" customHeight="1">
       <c r="A65" s="1" t="inlineStr">
         <is>
-          <t>〜経由で、〜の方法で</t>
+          <t>何か〜する…なもの</t>
         </is>
       </c>
       <c r="B65" s="1" t="inlineStr">
         <is>
-          <t>by way of ~</t>
+          <t>something ... to do</t>
         </is>
       </c>
     </row>
     <row r="66" ht="20" customHeight="1">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>〜に当てはまる</t>
+          <t>Aに〜を案内する</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>be true of ~</t>
+          <t>show A around ~</t>
         </is>
       </c>
     </row>
     <row r="67" ht="20" customHeight="1">
       <c r="A67" s="1" t="inlineStr">
         <is>
-          <t>〜から独立している</t>
+          <t>意志に反して</t>
         </is>
       </c>
       <c r="B67" s="1" t="inlineStr">
         <is>
-          <t>be independent of ~</t>
+          <t>against one's will</t>
         </is>
       </c>
     </row>
     <row r="68" ht="20" customHeight="1">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>他方では、一方で</t>
+          <t>〜の心に訴える、〜に訴える</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>on the other hand</t>
+          <t>appeal to ~</t>
         </is>
       </c>
     </row>
     <row r="69" ht="20" customHeight="1">
       <c r="A69" s="1" t="inlineStr">
         <is>
-          <t>AにBを供給する［提供する］</t>
+          <t>せいぜい、最大でも</t>
         </is>
       </c>
       <c r="B69" s="1" t="inlineStr">
         <is>
-          <t>provide A with B</t>
+          <t>at (the) most</t>
         </is>
       </c>
     </row>
     <row r="70" ht="20" customHeight="1">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>〜に関して</t>
+          <t>詳細に、（長い時間の末）ついに</t>
         </is>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>as to ~</t>
+          <t>at length</t>
         </is>
       </c>
     </row>
     <row r="71" ht="20" customHeight="1">
       <c r="A71" s="1" t="inlineStr">
         <is>
-          <t>〜につながる、〜を引き起こす</t>
+          <t>〜の危険を冒して</t>
         </is>
       </c>
       <c r="B71" s="1" t="inlineStr">
         <is>
-          <t>lead to ~</t>
+          <t>at the risk of ~</t>
         </is>
       </c>
     </row>
     <row r="72" ht="20" customHeight="1">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>Aを防ぐ</t>
+          <t>〜する能力がある、〜できる</t>
         </is>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>prevent A</t>
+          <t>be capable of doing</t>
         </is>
       </c>
     </row>
     <row r="73" ht="20" customHeight="1">
       <c r="A73" s="1" t="inlineStr">
         <is>
-          <t>AをBのせいにする</t>
+          <t>〜から解放されている</t>
         </is>
       </c>
       <c r="B73" s="1" t="inlineStr">
         <is>
-          <t>attribute A to B</t>
+          <t>be free from ~</t>
         </is>
       </c>
     </row>
     <row r="74" ht="20" customHeight="1">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>〜をよく知っている、〜に精通している</t>
+          <t>〜のことを感謝している</t>
         </is>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>be familiar with ~</t>
+          <t>be grateful for ~</t>
         </is>
       </c>
     </row>
     <row r="75" ht="20" customHeight="1">
       <c r="A75" s="1" t="inlineStr">
         <is>
-          <t>〜に適応する［慣れる］</t>
+          <t>〜から独立している</t>
         </is>
       </c>
       <c r="B75" s="1" t="inlineStr">
         <is>
-          <t>adapt to ~</t>
+          <t>be independent of ~</t>
         </is>
       </c>
     </row>
     <row r="76" ht="20" customHeight="1">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>〜に不可欠である</t>
+          <t>〜をねたんんでいる</t>
         </is>
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>be essential for ~</t>
+          <t>be jealous of ~</t>
         </is>
       </c>
     </row>
     <row r="77" ht="20" customHeight="1">
       <c r="A77" s="1" t="inlineStr">
         <is>
-          <t>Aを考慮に入れる</t>
+          <t>故障している</t>
         </is>
       </c>
       <c r="B77" s="1" t="inlineStr">
         <is>
-          <t>take A into account</t>
+          <t>be out of order</t>
         </is>
       </c>
     </row>
     <row r="78" ht="20" customHeight="1">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>習慣である</t>
+          <t>問題にならない、あり得ない</t>
         </is>
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>be custom</t>
+          <t>be out of the question</t>
         </is>
       </c>
     </row>
     <row r="79" ht="20" customHeight="1">
       <c r="A79" s="1" t="inlineStr">
         <is>
-          <t>〜という結果になる</t>
+          <t>〜が苦手である、〜が下手である</t>
         </is>
       </c>
       <c r="B79" s="1" t="inlineStr">
         <is>
-          <t>result in ~</t>
+          <t>be poor [bad] at ~</t>
         </is>
       </c>
     </row>
     <row r="80" ht="20" customHeight="1">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>〜から成る、〜で構成されている</t>
+          <t>〜にうんざりしている</t>
         </is>
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>consist of ~</t>
+          <t>be sick of ~</t>
         </is>
       </c>
     </row>
     <row r="81" ht="20" customHeight="1">
       <c r="A81" s="1" t="inlineStr">
         <is>
-          <t>〜の基本である</t>
+          <t>〜を確信している</t>
         </is>
       </c>
       <c r="B81" s="1" t="inlineStr">
         <is>
-          <t>be basic to ~</t>
+          <t>be sure of [about] ~</t>
         </is>
       </c>
     </row>
     <row r="82" ht="20" customHeight="1">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>〜の点から、〜に関して</t>
+          <t>〜をばらばらにする</t>
         </is>
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>in terms of ~</t>
+          <t>break up ~</t>
         </is>
       </c>
     </row>
     <row r="83" ht="20" customHeight="1">
       <c r="A83" s="1" t="inlineStr">
         <is>
-          <t>AとBを区別する</t>
+          <t>〜を育てる</t>
         </is>
       </c>
       <c r="B83" s="1" t="inlineStr">
         <is>
-          <t>distinguish A from B</t>
+          <t>bring up ~</t>
         </is>
       </c>
     </row>
     <row r="84" ht="20" customHeight="1">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>〜から切り離されている</t>
+          <t>暗記して</t>
         </is>
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>be separate from ~</t>
+          <t>by heart</t>
         </is>
       </c>
     </row>
     <row r="85" ht="20" customHeight="1">
       <c r="A85" s="1" t="inlineStr">
         <is>
-          <t>〜に関係なく［かかわらず］</t>
+          <t>〜を心配する、〜に関心を持つ</t>
         </is>
       </c>
       <c r="B85" s="1" t="inlineStr">
         <is>
-          <t>regardless of ~</t>
+          <t>care about ~</t>
         </is>
       </c>
     </row>
     <row r="86" ht="20" customHeight="1">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>AからBを奪う</t>
+          <t>〜なしで済ます</t>
         </is>
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>deprive A of B</t>
+          <t>do without ~</t>
         </is>
       </c>
     </row>
     <row r="87" ht="20" customHeight="1">
       <c r="A87" s="1" t="inlineStr">
         <is>
-          <t>〜にとって明らかである</t>
+          <t>くつろぐ、気が休まる</t>
         </is>
       </c>
       <c r="B87" s="1" t="inlineStr">
         <is>
-          <t>be clear to ~</t>
+          <t>feel at home</t>
         </is>
       </c>
     </row>
     <row r="88" ht="20" customHeight="1">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>〜と比べて</t>
+          <t>〜を気の毒に思う、〜のことですまないと思う</t>
         </is>
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>in comparison with ~</t>
+          <t>feel sorry for ~</t>
         </is>
       </c>
     </row>
     <row r="89" ht="20" customHeight="1">
       <c r="A89" s="1" t="inlineStr">
         <is>
-          <t>具体的である、特定の</t>
+          <t>気分転換に、目先を変えて</t>
         </is>
       </c>
       <c r="B89" s="1" t="inlineStr">
         <is>
-          <t>be specific</t>
+          <t>for a change</t>
         </is>
       </c>
     </row>
     <row r="90" ht="20" customHeight="1">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>〜と対照的に</t>
+          <t>〜から離れる</t>
         </is>
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>in contrast to ~</t>
+          <t>get away from ~</t>
         </is>
       </c>
     </row>
     <row r="91" ht="20" customHeight="1">
       <c r="A91" s="1" t="inlineStr">
         <is>
-          <t>〜に由来する</t>
+          <t>〜へ向かう</t>
         </is>
       </c>
       <c r="B91" s="1" t="inlineStr">
         <is>
-          <t>derive from ~</t>
+          <t>head for ~</t>
         </is>
       </c>
     </row>
     <row r="92" ht="20" customHeight="1">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>〜に適している</t>
+          <t>ある意味では</t>
         </is>
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>be appropriate for ~</t>
+          <t>in a sense</t>
         </is>
       </c>
     </row>
     <row r="93" ht="20" customHeight="1">
       <c r="A93" s="1" t="inlineStr">
         <is>
-          <t>個々の、独特の</t>
+          <t>それとは対照的に</t>
         </is>
       </c>
       <c r="B93" s="1" t="inlineStr">
         <is>
-          <t>be individual</t>
+          <t>in contrast</t>
         </is>
       </c>
     </row>
     <row r="94" ht="20" customHeight="1">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>〜と同一である</t>
+          <t>体調が良くて</t>
         </is>
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>be identical with ~</t>
+          <t>in shape</t>
         </is>
       </c>
     </row>
     <row r="95" ht="20" customHeight="1">
       <c r="A95" s="1" t="inlineStr">
         <is>
-          <t>〜に関して</t>
+          <t>〜から目を離さない</t>
         </is>
       </c>
       <c r="B95" s="1" t="inlineStr">
         <is>
-          <t>with respect to ~</t>
+          <t>keep an eye on ~</t>
         </is>
       </c>
     </row>
     <row r="96" ht="20" customHeight="1">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>〜にとって動的である</t>
+          <t>約束を守る</t>
         </is>
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>be dynamic to ~</t>
+          <t>keep one's promise [word]</t>
         </is>
       </c>
     </row>
     <row r="97" ht="20" customHeight="1">
       <c r="A97" s="1" t="inlineStr">
         <is>
-          <t>AからBを奪う</t>
+          <t>〜を尊敬する</t>
         </is>
       </c>
       <c r="B97" s="1" t="inlineStr">
         <is>
-          <t>rob A of B</t>
+          <t>look up to ~</t>
         </is>
       </c>
     </row>
     <row r="98" ht="20" customHeight="1">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>〜に適している</t>
+          <t>自制を失う</t>
         </is>
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>be appropriate to ~</t>
+          <t>lose control</t>
         </is>
       </c>
     </row>
     <row r="99" ht="20" customHeight="1">
       <c r="A99" s="1" t="inlineStr">
         <is>
-          <t>〜から独立している</t>
+          <t>バランスを崩す</t>
         </is>
       </c>
       <c r="B99" s="1" t="inlineStr">
         <is>
-          <t>be independent from ~</t>
+          <t>lose one's balance</t>
         </is>
       </c>
     </row>
     <row r="100" ht="20" customHeight="1">
       <c r="A100" s="2" t="inlineStr">
         <is>
-          <t>〜に応えて、〜に反応して</t>
+          <t>くつろぐ</t>
         </is>
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>in response to ~</t>
+          <t>make oneself at home</t>
         </is>
       </c>
     </row>
